--- a/test/inputs/spectramax.xlsx
+++ b/test/inputs/spectramax.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/qr24461/.julia/dev/esm/test/inputs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/qr24461/.julia/dev/Longwing/test/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{475A3CEA-DB5F-9044-A5B2-2D9C31F001D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8A94DC0-9695-DD43-8DC1-605638C89F45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17440" activeTab="4" xr2:uid="{7C37CC98-1F4A-4A36-93A3-A48642CDB423}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17440" activeTab="1" xr2:uid="{7C37CC98-1F4A-4A36-93A3-A48642CDB423}"/>
   </bookViews>
   <sheets>
     <sheet name="Samples" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
   <si>
     <t>Plate</t>
   </si>
@@ -106,6 +106,30 @@
   </si>
   <si>
     <t>abs700</t>
+  </si>
+  <si>
+    <t>535_485</t>
+  </si>
+  <si>
+    <t>flu</t>
+  </si>
+  <si>
+    <t>flu1</t>
+  </si>
+  <si>
+    <t>flu2</t>
+  </si>
+  <si>
+    <t>flu3</t>
+  </si>
+  <si>
+    <t>530_485_1</t>
+  </si>
+  <si>
+    <t>530_485_2</t>
+  </si>
+  <si>
+    <t>530_485_3</t>
   </si>
 </sst>
 </file>
@@ -569,7 +593,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DA707B9-0BE9-45E5-A5EE-A3873F0594F1}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
@@ -597,6 +621,38 @@
       </c>
       <c r="B3" t="s">
         <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
